--- a/Pruebas cohorte general II/resultados_v2_n3.xlsx
+++ b/Pruebas cohorte general II/resultados_v2_n3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\TFG\Pruebas cohorte general II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC46A2C-D0DE-4715-9923-1BECE69D00CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74187427-0CA0-4B23-ACDA-8A852FAE7C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="750" yWindow="525" windowWidth="27510" windowHeight="12990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Modelo</t>
   </si>
@@ -51,7 +51,28 @@
     <t>LightGBM</t>
   </si>
   <si>
-    <t>Dif respecto a I</t>
+    <t>error</t>
+  </si>
+  <si>
+    <t>0.7508 ± 0.0117</t>
+  </si>
+  <si>
+    <t>0.7742 ± 0.0085</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>0.7495</t>
+  </si>
+  <si>
+    <t>0.7745</t>
+  </si>
+  <si>
+    <t>0.7535</t>
+  </si>
+  <si>
+    <t>0.7732</t>
   </si>
 </sst>
 </file>
@@ -109,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -132,22 +153,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,9 +170,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -467,33 +474,60 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
